--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.17004069445655</v>
+        <v>4.90263161284919</v>
       </c>
       <c r="D2" t="n">
-        <v>39.06248505621515</v>
+        <v>6.347653821634962</v>
       </c>
       <c r="E2" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F2" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.90129586277091</v>
+        <v>2.096460577700273</v>
       </c>
       <c r="D3" t="n">
-        <v>12.58688451445814</v>
+        <v>2.045368733599447</v>
       </c>
       <c r="E3" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F3" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.43048416076861</v>
+        <v>5.1074536761249</v>
       </c>
       <c r="D4" t="n">
-        <v>31.64334720412416</v>
+        <v>5.142043920670177</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F4" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.28696223772863</v>
+        <v>4.434131363630903</v>
       </c>
       <c r="D5" t="n">
-        <v>27.73814642516577</v>
+        <v>4.507448794089438</v>
       </c>
       <c r="E5" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F5" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.42790330192367</v>
+        <v>7.057034286562597</v>
       </c>
       <c r="D6" t="n">
-        <v>43.28939798853216</v>
+        <v>7.034527173136476</v>
       </c>
       <c r="E6" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F6" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.18992541412263</v>
+        <v>4.580862879794928</v>
       </c>
       <c r="D7" t="n">
-        <v>28.06653405688894</v>
+        <v>4.560811784244453</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F7" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>58.61527482091899</v>
+        <v>9.524982158399336</v>
       </c>
       <c r="D8" t="n">
-        <v>58.54430231250853</v>
+        <v>9.513449125782637</v>
       </c>
       <c r="E8" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F8" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.65099075453651</v>
+        <v>7.093285997612183</v>
       </c>
       <c r="D9" t="n">
-        <v>43.59396340761314</v>
+        <v>7.084019053737135</v>
       </c>
       <c r="E9" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F9" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.09313299676085</v>
+        <v>8.952634111973639</v>
       </c>
       <c r="D10" t="n">
-        <v>55.04653444739415</v>
+        <v>8.945061847701551</v>
       </c>
       <c r="E10" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F10" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.33113019304449</v>
+        <v>3.953808656369729</v>
       </c>
       <c r="D11" t="n">
-        <v>24.36910564501299</v>
+        <v>3.959979667314611</v>
       </c>
       <c r="E11" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F11" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.88041222172681</v>
+        <v>4.530566986030606</v>
       </c>
       <c r="D12" t="n">
-        <v>28.03953240397101</v>
+        <v>4.556424015645289</v>
       </c>
       <c r="E12" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F12" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>68.29570358636019</v>
+        <v>11.09805183278353</v>
       </c>
       <c r="D13" t="n">
-        <v>68.44584411878631</v>
+        <v>11.12244966930278</v>
       </c>
       <c r="E13" t="n">
-        <v>15.6236758011323</v>
+        <v>2.538847317684</v>
       </c>
       <c r="F13" t="n">
-        <v>15.4746935630128</v>
+        <v>2.51463770398958</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
